--- a/course-design-2/outputs/tables/ch4/27_recruitment_time_field_audit.xlsx
+++ b/course-design-2/outputs/tables/ch4/27_recruitment_time_field_audit.xlsx
@@ -16,7 +16,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_同岗位多值统计" sheetId="7" state="visible" r:id="rId7"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_异常值清单" sheetId="8" state="visible" r:id="rId8"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_远期默认值" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_口径对照" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_统计范围对照" sheetId="10" state="visible" r:id="rId10"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>

--- a/course-design-2/outputs/tables/ch4/27_recruitment_time_field_audit.xlsx
+++ b/course-design-2/outputs/tables/ch4/27_recruitment_time_field_audit.xlsx
@@ -478,7 +478,6 @@
       <c r="B3" t="n">
         <v>17144</v>
       </c>
-      <c r="C3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -489,7 +488,6 @@
       <c r="B4" t="n">
         <v>1</v>
       </c>
-      <c r="C4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -500,7 +498,6 @@
       <c r="B5" t="n">
         <v>0.99998256</v>
       </c>
-      <c r="C5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -511,7 +508,6 @@
       <c r="B6" t="n">
         <v>172052</v>
       </c>
-      <c r="C6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -541,7 +537,6 @@
           <t>2026-04-22 14:15:56</t>
         </is>
       </c>
-      <c r="C8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -552,7 +547,6 @@
       <c r="B9" t="n">
         <v>19040</v>
       </c>
-      <c r="C9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -565,7 +559,6 @@
           <t>2026-03-21 00:00:00</t>
         </is>
       </c>
-      <c r="C10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -578,7 +571,6 @@
           <t>2028-11-22 00:00:00</t>
         </is>
       </c>
-      <c r="C11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -604,7 +596,6 @@
       <c r="B13" t="n">
         <v>465</v>
       </c>
-      <c r="C13" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
@@ -615,7 +606,6 @@
       <c r="B14" t="n">
         <v>416</v>
       </c>
-      <c r="C14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
@@ -626,7 +616,6 @@
       <c r="B15" t="n">
         <v>407</v>
       </c>
-      <c r="C15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
@@ -637,7 +626,6 @@
       <c r="B16" t="n">
         <v>0</v>
       </c>
-      <c r="C16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
@@ -663,7 +651,6 @@
       <c r="B18" t="n">
         <v>852</v>
       </c>
-      <c r="C18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
@@ -691,7 +678,6 @@
           <t>2026-03-22 00:33:41 ~ 2026-04-22 19:31:07</t>
         </is>
       </c>
-      <c r="C20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
@@ -702,7 +688,6 @@
       <c r="B21" t="n">
         <v>172055</v>
       </c>
-      <c r="C21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
@@ -12840,7 +12825,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
